--- a/Develop/Assets/Resources/Data/game_data.xlsx
+++ b/Develop/Assets/Resources/Data/game_data.xlsx
@@ -2,8 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_catalog" sheetId="1" r:id="R3a6e911efc93404a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stage_list" sheetId="2" r:id="Rbddfc99131f44c77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_catalog" sheetId="1" r:id="Rf35ef65ba78a4e67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stage_list" sheetId="2" r:id="R6e6ad0fcf2d24a69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievement" sheetId="3" r:id="Reb355395ea484b70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievement_reward" sheetId="4" r:id="R5e8f77b26d4e4150"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="level_reward" sheetId="5" r:id="R413fca8300cc4de5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="user" sheetId="6" r:id="R5933228112414d17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="achievement_condition" sheetId="7" r:id="R292473e4b73741ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="special_reward" sheetId="8" r:id="R282f919d2ffd4ef9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -35,7 +41,7 @@
       <x:name val="Malgun Gothic"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -52,6 +58,11 @@
         <x:fgColor rgb="FFF0F4F8"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF23344B"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -59,7 +70,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -88,6 +99,12 @@
     </x:xf>
     <x:xf numFmtId="201" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -124,6 +141,82 @@
     <x:tableColumn id="4" name="등장 npc"/>
     <x:tableColumn id="5" name="npc 대사"/>
     <x:tableColumn id="6" name="npc 속성"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RewardData_Achievement" displayName="RewardData_Achievement" ref="A1:B9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:B9"/>
+  <x:tableColumns count="2">
+    <x:tableColumn id="1" name="id"/>
+    <x:tableColumn id="2" name="name"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RewardData_Achievement_reward" displayName="RewardData_Achievement_reward" ref="A1:E25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E25"/>
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="id"/>
+    <x:tableColumn id="2" name="items_id"/>
+    <x:tableColumn id="3" name="info"/>
+    <x:tableColumn id="4" name="level_id"/>
+    <x:tableColumn id="5" name="amount"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="RewardData_level_reward" displayName="RewardData_level_reward" ref="A1:D45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D45"/>
+  <x:tableColumns count="4">
+    <x:tableColumn id="1" name="id"/>
+    <x:tableColumn id="2" name="lv_num"/>
+    <x:tableColumn id="3" name="items_id"/>
+    <x:tableColumn id="4" name="amount"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RewardData_user" displayName="RewardData_user" ref="A1:D2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D2"/>
+  <x:tableColumns count="4">
+    <x:tableColumn id="1" name="id"/>
+    <x:tableColumn id="2" name="name"/>
+    <x:tableColumn id="3" name="is_get_lm_reward"/>
+    <x:tableColumn id="4" name="is_get_lv_reward"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="RewardData_achievement_condition" displayName="RewardData_achievement_condition" ref="A1:C9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:C9"/>
+  <x:tableColumns count="3">
+    <x:tableColumn id="1" name="id"/>
+    <x:tableColumn id="2" name="metric"/>
+    <x:tableColumn id="3" name="target"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="RewardData_special_reward" displayName="RewardData_special_reward" ref="A1:D4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D4"/>
+  <x:tableColumns count="4">
+    <x:tableColumn id="1" name="id"/>
+    <x:tableColumn id="2" name="kind"/>
+    <x:tableColumn id="3" name="items_id"/>
+    <x:tableColumn id="4" name="amount"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1063,7 +1156,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6daec503fb714f69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e5f5995209541e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1323,7 +1416,1423 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72a79bd1a1d5445b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e7d8fd519664631"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11.25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="37.5" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="12" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B1" s="12" t="str">
+        <x:v>name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="str">
+        <x:v>첫 배틀의 기억</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="str">
+        <x:v>예선 돌파</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="str">
+        <x:v>본선 돌파</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="str">
+        <x:v>뉴에리두 챔피언</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="28" customHeight="1">
+      <x:c r="A6" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="str">
+        <x:v>첫 번째 파티</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="28" customHeight="1">
+      <x:c r="A7" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="2" t="str">
+        <x:v>든든한 동료들</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="28" customHeight="1">
+      <x:c r="A8" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="str">
+        <x:v>방부 도감 완성</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="28" customHeight="1">
+      <x:c r="A9" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="str">
+        <x:v>각성의 순간</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd46697f62fe4432f"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12.5" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="12" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B1" s="12" t="str">
+        <x:v>items_id</x:v>
+      </x:c>
+      <x:c r="C1" s="12" t="str">
+        <x:v>info</x:v>
+      </x:c>
+      <x:c r="D1" s="12" t="str">
+        <x:v>level_id</x:v>
+      </x:c>
+      <x:c r="E1" s="12" t="str">
+        <x:v>amount</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="str">
+        <x:v>첫 배틀의 기억 보상</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="str">
+        <x:v>첫 배틀의 기억 보상</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="str">
+        <x:v>첫 배틀의 기억 보상</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="2" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="str">
+        <x:v>예선 돌파 보상</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E5" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="28" customHeight="1">
+      <x:c r="A6" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="str">
+        <x:v>예선 돌파 보상</x:v>
+      </x:c>
+      <x:c r="D6" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E6" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="28" customHeight="1">
+      <x:c r="A7" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="str">
+        <x:v>예선 돌파 보상</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E7" s="2" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="28" customHeight="1">
+      <x:c r="A8" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="str">
+        <x:v>본선 돌파 보상</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="28" customHeight="1">
+      <x:c r="A9" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="str">
+        <x:v>본선 돌파 보상</x:v>
+      </x:c>
+      <x:c r="D9" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="28" customHeight="1">
+      <x:c r="A10" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="str">
+        <x:v>본선 돌파 보상</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="2" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="28" customHeight="1">
+      <x:c r="A11" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="str">
+        <x:v>뉴에리두 챔피언 보상</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="28" customHeight="1">
+      <x:c r="A12" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="str">
+        <x:v>뉴에리두 챔피언 보상</x:v>
+      </x:c>
+      <x:c r="D12" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E12" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="28" customHeight="1">
+      <x:c r="A13" s="2" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="str">
+        <x:v>뉴에리두 챔피언 보상</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E13" s="2" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="28" customHeight="1">
+      <x:c r="A14" s="2" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="str">
+        <x:v>첫 번째 파티 보상</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E14" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="28" customHeight="1">
+      <x:c r="A15" s="2" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C15" s="2" t="str">
+        <x:v>첫 번째 파티 보상</x:v>
+      </x:c>
+      <x:c r="D15" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E15" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="28" customHeight="1">
+      <x:c r="A16" s="2" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B16" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C16" s="2" t="str">
+        <x:v>첫 번째 파티 보상</x:v>
+      </x:c>
+      <x:c r="D16" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E16" s="2" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="28" customHeight="1">
+      <x:c r="A17" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="2" t="str">
+        <x:v>든든한 동료들 보상</x:v>
+      </x:c>
+      <x:c r="D17" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E17" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="28" customHeight="1">
+      <x:c r="A18" s="2" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B18" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C18" s="2" t="str">
+        <x:v>든든한 동료들 보상</x:v>
+      </x:c>
+      <x:c r="D18" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E18" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="28" customHeight="1">
+      <x:c r="A19" s="2" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B19" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C19" s="2" t="str">
+        <x:v>든든한 동료들 보상</x:v>
+      </x:c>
+      <x:c r="D19" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E19" s="2" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="28" customHeight="1">
+      <x:c r="A20" s="2" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B20" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C20" s="2" t="str">
+        <x:v>방부 도감 완성 보상</x:v>
+      </x:c>
+      <x:c r="D20" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E20" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="28" customHeight="1">
+      <x:c r="A21" s="2" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B21" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C21" s="2" t="str">
+        <x:v>방부 도감 완성 보상</x:v>
+      </x:c>
+      <x:c r="D21" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E21" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="28" customHeight="1">
+      <x:c r="A22" s="2" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B22" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C22" s="2" t="str">
+        <x:v>방부 도감 완성 보상</x:v>
+      </x:c>
+      <x:c r="D22" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E22" s="2" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="28" customHeight="1">
+      <x:c r="A23" s="2" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B23" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C23" s="2" t="str">
+        <x:v>각성의 순간 보상</x:v>
+      </x:c>
+      <x:c r="D23" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E23" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="28" customHeight="1">
+      <x:c r="A24" s="2" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B24" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C24" s="2" t="str">
+        <x:v>각성의 순간 보상</x:v>
+      </x:c>
+      <x:c r="D24" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E24" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="28" customHeight="1">
+      <x:c r="A25" s="2" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B25" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C25" s="2" t="str">
+        <x:v>각성의 순간 보상</x:v>
+      </x:c>
+      <x:c r="D25" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E25" s="2" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f4448a132ef422d"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.5" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="12" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B1" s="12" t="str">
+        <x:v>lv_num</x:v>
+      </x:c>
+      <x:c r="C1" s="12" t="str">
+        <x:v>items_id</x:v>
+      </x:c>
+      <x:c r="D1" s="12" t="str">
+        <x:v>amount</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="28" customHeight="1">
+      <x:c r="A6" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="28" customHeight="1">
+      <x:c r="A7" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="28" customHeight="1">
+      <x:c r="A8" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="28" customHeight="1">
+      <x:c r="A9" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D9" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="28" customHeight="1">
+      <x:c r="A10" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="28" customHeight="1">
+      <x:c r="A11" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="28" customHeight="1">
+      <x:c r="A12" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D12" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="28" customHeight="1">
+      <x:c r="A13" s="2" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="28" customHeight="1">
+      <x:c r="A14" s="2" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="28" customHeight="1">
+      <x:c r="A15" s="2" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C15" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D15" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="28" customHeight="1">
+      <x:c r="A16" s="2" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B16" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C16" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D16" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="28" customHeight="1">
+      <x:c r="A17" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C17" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D17" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="28" customHeight="1">
+      <x:c r="A18" s="2" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B18" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C18" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D18" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="28" customHeight="1">
+      <x:c r="A19" s="2" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B19" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C19" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D19" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="28" customHeight="1">
+      <x:c r="A20" s="2" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B20" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C20" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D20" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="28" customHeight="1">
+      <x:c r="A21" s="2" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B21" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C21" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D21" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="28" customHeight="1">
+      <x:c r="A22" s="2" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B22" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C22" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D22" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="28" customHeight="1">
+      <x:c r="A23" s="2" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B23" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C23" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D23" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="28" customHeight="1">
+      <x:c r="A24" s="2" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B24" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C24" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D24" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="28" customHeight="1">
+      <x:c r="A25" s="2" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B25" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C25" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D25" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="28" customHeight="1">
+      <x:c r="A26" s="2" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B26" s="2" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C26" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D26" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="28" customHeight="1">
+      <x:c r="A27" s="2" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B27" s="2" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C27" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D27" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="28" customHeight="1">
+      <x:c r="A28" s="2" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B28" s="2" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C28" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D28" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="28" customHeight="1">
+      <x:c r="A29" s="2" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B29" s="2" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C29" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D29" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="28" customHeight="1">
+      <x:c r="A30" s="2" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B30" s="2" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C30" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D30" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="28" customHeight="1">
+      <x:c r="A31" s="2" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B31" s="2" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C31" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D31" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="28" customHeight="1">
+      <x:c r="A32" s="2" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B32" s="2" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C32" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D32" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="28" customHeight="1">
+      <x:c r="A33" s="2" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B33" s="2" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C33" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D33" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="28" customHeight="1">
+      <x:c r="A34" s="2" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B34" s="2" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C34" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D34" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="28" customHeight="1">
+      <x:c r="A35" s="2" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B35" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C35" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D35" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="28" customHeight="1">
+      <x:c r="A36" s="2" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B36" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C36" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D36" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="28" customHeight="1">
+      <x:c r="A37" s="2" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B37" s="2" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C37" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D37" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="28" customHeight="1">
+      <x:c r="A38" s="2" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B38" s="2" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C38" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D38" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="28" customHeight="1">
+      <x:c r="A39" s="2" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B39" s="2" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C39" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D39" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="28" customHeight="1">
+      <x:c r="A40" s="2" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B40" s="2" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C40" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D40" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="28" customHeight="1">
+      <x:c r="A41" s="2" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B41" s="2" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C41" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D41" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="28" customHeight="1">
+      <x:c r="A42" s="2" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B42" s="2" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C42" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D42" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="28" customHeight="1">
+      <x:c r="A43" s="2" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B43" s="2" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C43" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D43" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="28" customHeight="1">
+      <x:c r="A44" s="2" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B44" s="2" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C44" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D44" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="28" customHeight="1">
+      <x:c r="A45" s="2" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B45" s="2" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C45" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D45" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0147673d02e448f"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="23.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23.1299991607666" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="12" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B1" s="12" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="C1" s="12" t="str">
+        <x:v>is_get_lm_reward</x:v>
+      </x:c>
+      <x:c r="D1" s="12" t="str">
+        <x:v>is_get_lv_reward</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="str">
+        <x:v>플레이어</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e7acc3cafe14194"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11.25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="23.75" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.75" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="12" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B1" s="12" t="str">
+        <x:v>metric</x:v>
+      </x:c>
+      <x:c r="C1" s="12" t="str">
+        <x:v>target</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="str">
+        <x:v>stage</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="str">
+        <x:v>stage</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="str">
+        <x:v>stage</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="str">
+        <x:v>stage</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="28" customHeight="1">
+      <x:c r="A6" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="str">
+        <x:v>collection</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="28" customHeight="1">
+      <x:c r="A7" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="2" t="str">
+        <x:v>collection</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="28" customHeight="1">
+      <x:c r="A8" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="str">
+        <x:v>collection</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="28" customHeight="1">
+      <x:c r="A9" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="str">
+        <x:v>evolution</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra072317317874b70"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.5" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="12" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B1" s="12" t="str">
+        <x:v>kind</x:v>
+      </x:c>
+      <x:c r="C1" s="12" t="str">
+        <x:v>items_id</x:v>
+      </x:c>
+      <x:c r="D1" s="12" t="str">
+        <x:v>amount</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="str">
+        <x:v>special</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="str">
+        <x:v>special</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="str">
+        <x:v>maxlevel</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re364cd50f25546de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Develop/Assets/Resources/Data/game_data.xlsx
+++ b/Develop/Assets/Resources/Data/game_data.xlsx
@@ -2,14 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_catalog" sheetId="1" r:id="Rf35ef65ba78a4e67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stage_list" sheetId="2" r:id="R6e6ad0fcf2d24a69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievement" sheetId="3" r:id="Reb355395ea484b70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievement_reward" sheetId="4" r:id="R5e8f77b26d4e4150"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="level_reward" sheetId="5" r:id="R413fca8300cc4de5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="user" sheetId="6" r:id="R5933228112414d17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="achievement_condition" sheetId="7" r:id="R292473e4b73741ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="special_reward" sheetId="8" r:id="R282f919d2ffd4ef9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_catalog" sheetId="1" r:id="R89f2c64aaa484aa9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stage_list" sheetId="2" r:id="Rc2106ad4b1da4d52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievement" sheetId="3" r:id="R922bb7459d254f7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievement_reward" sheetId="4" r:id="Rb0ede62619414f7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="level_reward" sheetId="5" r:id="Rc9832485f1a840b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="user" sheetId="6" r:id="Receffa4c7a914169"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="achievement_condition" sheetId="7" r:id="Rc6f29de27e154730"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="special_reward" sheetId="8" r:id="R06dc69bb25324090"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pause_list" sheetId="9" r:id="Radb91e0c891a4cbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="party" sheetId="10" r:id="R53d3d4877a9b49d5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24,7 +26,7 @@
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -40,8 +42,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Malgun Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Malgun Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -63,6 +75,11 @@
         <x:fgColor rgb="FF23344B"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF20324D"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -70,7 +87,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -105,6 +122,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1156,8 +1179,93 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e5f5995209541e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra02bb1d736cd4a6f"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B1" s="15" t="str">
+        <x:v>uid</x:v>
+      </x:c>
+      <x:c r="C1" s="15" t="str">
+        <x:v>bid</x:v>
+      </x:c>
+      <x:c r="D1" s="15" t="str">
+        <x:v>is_on_field</x:v>
+      </x:c>
+      <x:c r="E1" s="15" t="str">
+        <x:v>hp</x:v>
+      </x:c>
+      <x:c r="F1" s="15" t="str">
+        <x:v>state</x:v>
+      </x:c>
+      <x:c r="G1" s="15" t="str">
+        <x:v>need_exp</x:v>
+      </x:c>
+      <x:c r="H1" s="15" t="str">
+        <x:v>current_exp</x:v>
+      </x:c>
+      <x:c r="I1" s="15" t="str">
+        <x:v>level</x:v>
+      </x:c>
+      <x:c r="J1" s="15" t="str">
+        <x:v>max_hp</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="13" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D2" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="13" t="n">
+        <x:v>808</x:v>
+      </x:c>
+      <x:c r="F2" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G2" s="13" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H2" s="13" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I2" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J2" s="13" t="n">
+        <x:v>808</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -1416,7 +1524,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e7d8fd519664631"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b72836acca84be5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1504,7 +1612,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd46697f62fe4432f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47bb444ac4db4721"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1948,7 +2056,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f4448a132ef422d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81f1fbca41e84640"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2596,7 +2704,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0147673d02e448f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4031de841c4b45ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2642,7 +2750,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e7acc3cafe14194"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f1819e182ea44e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2758,7 +2866,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra072317317874b70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfccce73a197544df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2832,7 +2940,80 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re364cd50f25546de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e3503f716e54eae"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="32" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="60" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="60" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B1" s="15" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="C1" s="15" t="str">
+        <x:v>info1</x:v>
+      </x:c>
+      <x:c r="D1" s="15" t="str">
+        <x:v>info2</x:v>
+      </x:c>
+      <x:c r="E1" s="15" t="str">
+        <x:v>info3</x:v>
+      </x:c>
+      <x:c r="F1" s="15" t="str">
+        <x:v>info4</x:v>
+      </x:c>
+      <x:c r="G1" s="15" t="str">
+        <x:v>info5</x:v>
+      </x:c>
+      <x:c r="H1" s="15" t="str">
+        <x:v>info6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="72" customHeight="1">
+      <x:c r="A2" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="16" t="str">
+        <x:v>챔피언 리그 상세</x:v>
+      </x:c>
+      <x:c r="C2" s="16" t="str">
+        <x:v>도전 목표</x:v>
+      </x:c>
+      <x:c r="D2" s="16" t="str">
+        <x:v>‘{npc}’와의 배틀에서 승리하기</x:v>
+      </x:c>
+      <x:c r="E2" s="16" t="str">
+        <x:v>{npc_dialogue}</x:v>
+      </x:c>
+      <x:c r="F2" s="16" t="str">
+        <x:v>주특기 간 상성 메커니즘</x:v>
+      </x:c>
+      <x:c r="G2" s="16" t="str">
+        <x:v>물리, 불, 얼음 주특기는 서로 순환하는 상성을 가집니다.
+물리는 불에, 불은 얼음에, 얼음은 물리에 강합니다.</x:v>
+      </x:c>
+      <x:c r="H2" s="16" t="str">
+        <x:v>전기, 에테르 주특기는 서로에게 약점이 되는 상성을 가집니다.
+전기는 에테르에게, 에테르는 전기에게 강합니다.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/Develop/Assets/Resources/Data/game_data.xlsx
+++ b/Develop/Assets/Resources/Data/game_data.xlsx
@@ -2,16 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_catalog" sheetId="1" r:id="R89f2c64aaa484aa9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stage_list" sheetId="2" r:id="Rc2106ad4b1da4d52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievement" sheetId="3" r:id="R922bb7459d254f7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Achievement_reward" sheetId="4" r:id="Rb0ede62619414f7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="level_reward" sheetId="5" r:id="Rc9832485f1a840b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="user" sheetId="6" r:id="Receffa4c7a914169"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="achievement_condition" sheetId="7" r:id="Rc6f29de27e154730"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="special_reward" sheetId="8" r:id="R06dc69bb25324090"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pause_list" sheetId="9" r:id="Radb91e0c891a4cbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="party" sheetId="10" r:id="R53d3d4877a9b49d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_list" sheetId="1" r:id="Re9d820edfdc24301"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stage_list" sheetId="2" r:id="Ra38d5493c03a4ac7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="achievement" sheetId="3" r:id="R38b83c1ee081479c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="achievement_reward" sheetId="4" r:id="Rade34b568ff14656"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="level_reward" sheetId="5" r:id="R8d854927b1294eb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="6" r:id="Raccd4f1b83434c32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="special_reward" sheetId="8" r:id="Rb7d6b5cc75b841b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pause_list" sheetId="9" r:id="Rddbaa74dfc604acd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="party" sheetId="10" r:id="Rdcb5d7bb8ef44782"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bangboo" sheetId="11" r:id="Rc4462bd0203646a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skills" sheetId="12" r:id="Rdeecbb86122c48c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +54,7 @@
       <x:name val="Malgun Gothic"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -80,6 +81,21 @@
         <x:fgColor rgb="FF20324D"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF20324D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF20324D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF20324D"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -87,7 +103,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -129,11 +145,76 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -170,11 +251,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RewardData_Achievement" displayName="RewardData_Achievement" ref="A1:B9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:B9"/>
-  <x:tableColumns count="2">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="RewardData_Achievement" displayName="RewardData_Achievement" ref="A1:D9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="4">
     <x:tableColumn id="1" name="id"/>
     <x:tableColumn id="2" name="name"/>
+    <x:tableColumn id="3" name="metric"/>
+    <x:tableColumn id="4" name="target"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -208,31 +290,24 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RewardData_user" displayName="RewardData_user" ref="A1:D2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D2"/>
-  <x:tableColumns count="4">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="RewardData_user" displayName="RewardData_user" ref="A1:J2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="10">
     <x:tableColumn id="1" name="id"/>
     <x:tableColumn id="2" name="name"/>
     <x:tableColumn id="3" name="is_get_lm_reward"/>
     <x:tableColumn id="4" name="is_get_lv_reward"/>
+    <x:tableColumn id="5" name="has_bangboo_11"/>
+    <x:tableColumn id="6" name="bangboo_11_lv"/>
+    <x:tableColumn id="7" name="has_bangboo_21"/>
+    <x:tableColumn id="8" name="bangboo_21_lv"/>
+    <x:tableColumn id="9" name="has_bangboo_31"/>
+    <x:tableColumn id="10" name="bangboo_31_lv"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="RewardData_achievement_condition" displayName="RewardData_achievement_condition" ref="A1:C9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:C9"/>
-  <x:tableColumns count="3">
-    <x:tableColumn id="1" name="id"/>
-    <x:tableColumn id="2" name="metric"/>
-    <x:tableColumn id="3" name="target"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="RewardData_special_reward" displayName="RewardData_special_reward" ref="A1:D4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:D4"/>
   <x:tableColumns count="4">
@@ -240,6 +315,33 @@
     <x:tableColumn id="2" name="kind"/>
     <x:tableColumn id="3" name="items_id"/>
     <x:tableColumn id="4" name="amount"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="bangboo_table" displayName="bangboo_table" ref="A1:F4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="id"/>
+    <x:tableColumn id="2" name="name"/>
+    <x:tableColumn id="3" name="type"/>
+    <x:tableColumn id="4" name="hp"/>
+    <x:tableColumn id="5" name="atk"/>
+    <x:tableColumn id="6" name="def"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="skills_table" displayName="skills_table" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="id"/>
+    <x:tableColumn id="2" name="bid"/>
+    <x:tableColumn id="3" name="name"/>
+    <x:tableColumn id="4" name="type"/>
+    <x:tableColumn id="5" name="max_num"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1179,7 +1281,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra02bb1d736cd4a6f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42a0e5ef5c1548d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1188,84 +1290,288 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="15" t="str">
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="24" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="B1" s="15" t="str">
-        <x:v>uid</x:v>
-      </x:c>
-      <x:c r="C1" s="15" t="str">
-        <x:v>bid</x:v>
-      </x:c>
-      <x:c r="D1" s="15" t="str">
-        <x:v>is_on_field</x:v>
-      </x:c>
-      <x:c r="E1" s="15" t="str">
+      <x:c r="B1" s="24" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="C1" s="24" t="str">
+        <x:v>type</x:v>
+      </x:c>
+      <x:c r="D1" s="24" t="str">
         <x:v>hp</x:v>
       </x:c>
-      <x:c r="F1" s="15" t="str">
-        <x:v>state</x:v>
-      </x:c>
-      <x:c r="G1" s="15" t="str">
-        <x:v>need_exp</x:v>
-      </x:c>
-      <x:c r="H1" s="15" t="str">
-        <x:v>current_exp</x:v>
-      </x:c>
-      <x:c r="I1" s="15" t="str">
-        <x:v>level</x:v>
-      </x:c>
-      <x:c r="J1" s="15" t="str">
-        <x:v>max_hp</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
+      <x:c r="E1" s="24" t="str">
+        <x:v>atk</x:v>
+      </x:c>
+      <x:c r="F1" s="24" t="str">
+        <x:v>def</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="13" t="n">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B2" s="13" t="str">
+        <x:v>봉투부</x:v>
       </x:c>
       <x:c r="C2" s="13" t="n">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D2" s="13" t="n">
-        <x:v>1</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="E2" s="13" t="n">
-        <x:v>808</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F2" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G2" s="13" t="n">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="H2" s="13" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="13" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B3" s="13" t="str">
+        <x:v>울보부</x:v>
+      </x:c>
+      <x:c r="C3" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D3" s="13" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="I2" s="13" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J2" s="13" t="n">
-        <x:v>808</x:v>
+      <x:c r="F3" s="13" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="13" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B4" s="13" t="str">
+        <x:v>펭귄부</x:v>
+      </x:c>
+      <x:c r="C4" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D4" s="13" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="E4" s="13" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F4" s="13" t="n">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb666ed8886e043ab"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="24" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B1" s="24" t="str">
+        <x:v>bid</x:v>
+      </x:c>
+      <x:c r="C1" s="24" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="D1" s="24" t="str">
+        <x:v>type</x:v>
+      </x:c>
+      <x:c r="E1" s="24" t="str">
+        <x:v>max_num</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="13" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B2" s="13" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C2" s="13" t="str">
+        <x:v>몸통박치기</x:v>
+      </x:c>
+      <x:c r="D2" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="13" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="13" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B3" s="13" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C3" s="13" t="str">
+        <x:v>봉투난타</x:v>
+      </x:c>
+      <x:c r="D3" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="13" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B4" s="13" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C4" s="13" t="str">
+        <x:v>응급수리</x:v>
+      </x:c>
+      <x:c r="D4" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="13" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="13" t="n">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B5" s="13" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="str">
+        <x:v>몸통박치기</x:v>
+      </x:c>
+      <x:c r="D5" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E5" s="13" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="13" t="n">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C6" s="13" t="str">
+        <x:v>불꽃탄</x:v>
+      </x:c>
+      <x:c r="D6" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E6" s="13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="13" t="n">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B7" s="13" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="str">
+        <x:v>응급수리</x:v>
+      </x:c>
+      <x:c r="D7" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="13" t="n">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B8" s="13" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="str">
+        <x:v>몸통박치기</x:v>
+      </x:c>
+      <x:c r="D8" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="13" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="13" t="n">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B9" s="13" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="str">
+        <x:v>얼음파동</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="13" t="n">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B10" s="13" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="str">
+        <x:v>응급수리</x:v>
+      </x:c>
+      <x:c r="D10" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="13" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15627457c3444c38"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -1524,7 +1830,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b72836acca84be5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbc8784a1b284d96"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1535,6 +1841,8 @@
   <x:cols>
     <x:col min="1" max="1" width="11.25" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="37.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -1544,6 +1852,12 @@
       <x:c r="B1" s="12" t="str">
         <x:v>name</x:v>
       </x:c>
+      <x:c r="C1" s="20" t="str">
+        <x:v>metric</x:v>
+      </x:c>
+      <x:c r="D1" s="20" t="str">
+        <x:v>target</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="2" t="n">
@@ -1552,6 +1866,12 @@
       <x:c r="B2" s="2" t="str">
         <x:v>첫 배틀의 기억</x:v>
       </x:c>
+      <x:c r="C2" s="17" t="str">
+        <x:v>stage</x:v>
+      </x:c>
+      <x:c r="D2" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="2" t="n">
@@ -1560,6 +1880,12 @@
       <x:c r="B3" s="2" t="str">
         <x:v>예선 돌파</x:v>
       </x:c>
+      <x:c r="C3" s="17" t="str">
+        <x:v>stage</x:v>
+      </x:c>
+      <x:c r="D3" s="17" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
       <x:c r="A4" s="2" t="n">
@@ -1567,6 +1893,12 @@
       </x:c>
       <x:c r="B4" s="2" t="str">
         <x:v>본선 돌파</x:v>
+      </x:c>
+      <x:c r="C4" s="17" t="str">
+        <x:v>stage</x:v>
+      </x:c>
+      <x:c r="D4" s="17" t="n">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
@@ -1576,6 +1908,12 @@
       <x:c r="B5" s="2" t="str">
         <x:v>뉴에리두 챔피언</x:v>
       </x:c>
+      <x:c r="C5" s="17" t="str">
+        <x:v>stage</x:v>
+      </x:c>
+      <x:c r="D5" s="17" t="n">
+        <x:v>11</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
       <x:c r="A6" s="2" t="n">
@@ -1584,6 +1922,12 @@
       <x:c r="B6" s="2" t="str">
         <x:v>첫 번째 파티</x:v>
       </x:c>
+      <x:c r="C6" s="17" t="str">
+        <x:v>collection</x:v>
+      </x:c>
+      <x:c r="D6" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
       <x:c r="A7" s="2" t="n">
@@ -1592,6 +1936,12 @@
       <x:c r="B7" s="2" t="str">
         <x:v>든든한 동료들</x:v>
       </x:c>
+      <x:c r="C7" s="17" t="str">
+        <x:v>collection</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
       <x:c r="A8" s="2" t="n">
@@ -1600,6 +1950,12 @@
       <x:c r="B8" s="2" t="str">
         <x:v>방부 도감 완성</x:v>
       </x:c>
+      <x:c r="C8" s="17" t="str">
+        <x:v>collection</x:v>
+      </x:c>
+      <x:c r="D8" s="17" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
       <x:c r="A9" s="2" t="n">
@@ -1608,11 +1964,17 @@
       <x:c r="B9" s="2" t="str">
         <x:v>각성의 순간</x:v>
       </x:c>
+      <x:c r="C9" s="17" t="str">
+        <x:v>evolution</x:v>
+      </x:c>
+      <x:c r="D9" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47bb444ac4db4721"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffa1f8c6f1f642e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2056,7 +2418,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81f1fbca41e84640"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51a29d678e2f4744"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2704,7 +3066,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4031de841c4b45ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c489f0cf0694e31"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2717,6 +3079,12 @@
     <x:col min="2" max="2" width="22.5" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="23.1299991607666" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="23.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -2732,6 +3100,24 @@
       <x:c r="D1" s="12" t="str">
         <x:v>is_get_lv_reward</x:v>
       </x:c>
+      <x:c r="E1" s="29" t="str">
+        <x:v>has_bangboo_11</x:v>
+      </x:c>
+      <x:c r="F1" s="29" t="str">
+        <x:v>bangboo_11_lv</x:v>
+      </x:c>
+      <x:c r="G1" s="29" t="str">
+        <x:v>has_bangboo_21</x:v>
+      </x:c>
+      <x:c r="H1" s="29" t="str">
+        <x:v>bangboo_21_lv</x:v>
+      </x:c>
+      <x:c r="I1" s="29" t="str">
+        <x:v>has_bangboo_31</x:v>
+      </x:c>
+      <x:c r="J1" s="29" t="str">
+        <x:v>bangboo_31_lv</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="2" t="n">
@@ -2744,134 +3130,36 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2" s="27" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F2" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G2" s="27" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H2" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I2" s="27" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J2" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f1819e182ea44e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R346428c3978f428b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="11.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="23.75" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="13.75" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="12" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="B1" s="12" t="str">
-        <x:v>metric</x:v>
-      </x:c>
-      <x:c r="C1" s="12" t="str">
-        <x:v>target</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="28" customHeight="1">
-      <x:c r="A2" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="str">
-        <x:v>stage</x:v>
-      </x:c>
-      <x:c r="C2" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="28" customHeight="1">
-      <x:c r="A3" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="str">
-        <x:v>stage</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="str">
-        <x:v>stage</x:v>
-      </x:c>
-      <x:c r="C4" s="2" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="28" customHeight="1">
-      <x:c r="A5" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="2" t="str">
-        <x:v>stage</x:v>
-      </x:c>
-      <x:c r="C5" s="2" t="n">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="28" customHeight="1">
-      <x:c r="A6" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="str">
-        <x:v>collection</x:v>
-      </x:c>
-      <x:c r="C6" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="28" customHeight="1">
-      <x:c r="A7" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B7" s="2" t="str">
-        <x:v>collection</x:v>
-      </x:c>
-      <x:c r="C7" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="28" customHeight="1">
-      <x:c r="A8" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B8" s="2" t="str">
-        <x:v>collection</x:v>
-      </x:c>
-      <x:c r="C8" s="2" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="28" customHeight="1">
-      <x:c r="A9" s="2" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B9" s="2" t="str">
-        <x:v>evolution</x:v>
-      </x:c>
-      <x:c r="C9" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfccce73a197544df"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -2940,12 +3228,12 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e3503f716e54eae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b0ff50953174f5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -3016,4 +3304,96 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="15" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B1" s="15" t="str">
+        <x:v>uid</x:v>
+      </x:c>
+      <x:c r="C1" s="15" t="str">
+        <x:v>bid</x:v>
+      </x:c>
+      <x:c r="D1" s="15" t="str">
+        <x:v>is_on_field</x:v>
+      </x:c>
+      <x:c r="E1" s="15" t="str">
+        <x:v>hp</x:v>
+      </x:c>
+      <x:c r="F1" s="15" t="str">
+        <x:v>state</x:v>
+      </x:c>
+      <x:c r="G1" s="15" t="str">
+        <x:v>need_exp</x:v>
+      </x:c>
+      <x:c r="H1" s="15" t="str">
+        <x:v>current_exp</x:v>
+      </x:c>
+      <x:c r="I1" s="15" t="str">
+        <x:v>level</x:v>
+      </x:c>
+      <x:c r="J1" s="15" t="str">
+        <x:v>max_hp</x:v>
+      </x:c>
+      <x:c r="K1" s="22" t="str">
+        <x:v>lv</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="13" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D2" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="13" t="n">
+        <x:v>808</x:v>
+      </x:c>
+      <x:c r="F2" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G2" s="13" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H2" s="13" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I2" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J2" s="13" t="n">
+        <x:v>808</x:v>
+      </x:c>
+      <x:c r="K2" s="17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/Develop/Assets/Resources/Data/game_data.xlsx
+++ b/Develop/Assets/Resources/Data/game_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\프로젝트\ZZZ_Event_Repo\Develop\Assets\Resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD46B00-D9C3-45E6-B20B-71A6070CF840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE69CEA7-82C6-46FE-B6C3-30E0999891E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="350" yWindow="1020" windowWidth="31590" windowHeight="17100" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="350" yWindow="1020" windowWidth="30410" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="users" sheetId="6" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="328">
   <si>
     <t>permanent</t>
   </si>
@@ -1112,6 +1112,93 @@
   <si>
     <t>int</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1번 스테이지 클리어 여부</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2번 스테이지 클리어 여부</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3번 스테이지 클리어 여부</t>
+  </si>
+  <si>
+    <t>4번 스테이지 클리어 여부</t>
+  </si>
+  <si>
+    <t>5번 스테이지 클리어 여부</t>
+  </si>
+  <si>
+    <t>6번 스테이지 클리어 여부</t>
+  </si>
+  <si>
+    <t>7번 스테이지 클리어 여부</t>
+  </si>
+  <si>
+    <t>8번 스테이지 클리어 여부</t>
+  </si>
+  <si>
+    <t>9번 스테이지 클리어 여부</t>
+  </si>
+  <si>
+    <t>10번 스테이지 클리어 여부</t>
+  </si>
+  <si>
+    <t>11번 스테이지 클리어 여부</t>
+  </si>
+  <si>
+    <t>12번 스테이지 클리어 여부</t>
+  </si>
+  <si>
+    <t>13번 스테이지 클리어 여부</t>
+  </si>
+  <si>
+    <t>14번 스테이지 클리어 여부</t>
+  </si>
+  <si>
+    <t>is_st1_clear</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_st2_clear</t>
+  </si>
+  <si>
+    <t>is_st3_clear</t>
+  </si>
+  <si>
+    <t>is_st4_clear</t>
+  </si>
+  <si>
+    <t>is_st5_clear</t>
+  </si>
+  <si>
+    <t>is_st6_clear</t>
+  </si>
+  <si>
+    <t>is_st7_clear</t>
+  </si>
+  <si>
+    <t>is_st8_clear</t>
+  </si>
+  <si>
+    <t>is_st9_clear</t>
+  </si>
+  <si>
+    <t>is_st10_clear</t>
+  </si>
+  <si>
+    <t>is_st11_clear</t>
+  </si>
+  <si>
+    <t>is_st12_clear</t>
+  </si>
+  <si>
+    <t>is_st13_clear</t>
+  </si>
+  <si>
+    <t>is_st14_clear</t>
   </si>
 </sst>
 </file>
@@ -1577,21 +1664,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:AE5"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="3" width="22.5" style="1" customWidth="1"/>
-    <col min="4" max="5" width="23.1640625" style="1" customWidth="1"/>
-    <col min="6" max="8" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.9140625" style="1" customWidth="1"/>
-    <col min="11" max="15" width="16.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="17.4140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.6640625" style="1"/>
+    <col min="4" max="19" width="23.1640625" style="1" customWidth="1"/>
+    <col min="20" max="22" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.9140625" style="1" customWidth="1"/>
+    <col min="25" max="29" width="16.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="17.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>170</v>
       </c>
@@ -1608,43 +1695,85 @@
         <v>193</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="T1" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:31">
       <c r="A2" s="4" t="s">
         <v>158</v>
       </c>
@@ -1661,43 +1790,85 @@
         <v>207</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="AA2" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="AB2" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="AC2" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="AD2" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="AE2" s="4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:31">
       <c r="A3" s="5" t="s">
         <v>159</v>
       </c>
@@ -1749,16 +1920,58 @@
       <c r="Q3" s="5" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="20" customHeight="1">
+      <c r="R3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="AC3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="AE3" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" ht="20" customHeight="1">
       <c r="A4" s="6">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="C4" s="6">
-        <v>3</v>
+      <c r="C4" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="D4" s="6">
         <v>0</v>
@@ -1766,44 +1979,86 @@
       <c r="E4" s="6">
         <v>0</v>
       </c>
-      <c r="F4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="20" customHeight="1">
+      <c r="F4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0</v>
+      </c>
+      <c r="L4" s="6">
+        <v>0</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6">
+        <v>0</v>
+      </c>
+      <c r="T4" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="V4" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" ht="20" customHeight="1">
       <c r="A5" s="9">
         <v>2</v>
       </c>
@@ -1819,40 +2074,82 @@
       <c r="E5" s="9">
         <v>0</v>
       </c>
-      <c r="F5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8" t="b">
+      <c r="F5" s="9">
+        <v>0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9">
+        <v>0</v>
+      </c>
+      <c r="L5" s="9">
+        <v>0</v>
+      </c>
+      <c r="M5" s="9">
+        <v>0</v>
+      </c>
+      <c r="N5" s="9">
+        <v>0</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0</v>
+      </c>
+      <c r="P5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0</v>
+      </c>
+      <c r="R5" s="9">
+        <v>0</v>
+      </c>
+      <c r="S5" s="9">
+        <v>0</v>
+      </c>
+      <c r="T5" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4169,10 +4466,10 @@
         <v>1</v>
       </c>
       <c r="I4" s="27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="27">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K4" s="20">
         <v>1</v>
@@ -4216,7 +4513,7 @@
         <v>5</v>
       </c>
       <c r="J5" s="10">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K5" s="14">
         <v>2</v>

--- a/Develop/Assets/Resources/Data/game_data.xlsx
+++ b/Develop/Assets/Resources/Data/game_data.xlsx
@@ -8,23 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\프로젝트\ZZZ_Event_Repo\Develop\Assets\Resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE69CEA7-82C6-46FE-B6C3-30E0999891E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D60209-86BB-4398-BE6C-ECE8D0CEFA7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="350" yWindow="1020" windowWidth="30410" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18250" yWindow="710" windowWidth="19150" windowHeight="16180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="users" sheetId="6" r:id="rId1"/>
-    <sheet name="items" sheetId="13" r:id="rId2"/>
-    <sheet name="event_list" sheetId="1" r:id="rId3"/>
-    <sheet name="stage_list" sheetId="2" r:id="rId4"/>
-    <sheet name="achievement" sheetId="3" r:id="rId5"/>
-    <sheet name="achievement_reward" sheetId="4" r:id="rId6"/>
-    <sheet name="level_reward" sheetId="5" r:id="rId7"/>
-    <sheet name="special_reward" sheetId="8" r:id="rId8"/>
-    <sheet name="pause_list" sheetId="9" r:id="rId9"/>
-    <sheet name="party" sheetId="10" r:id="rId10"/>
-    <sheet name="bangboo" sheetId="11" r:id="rId11"/>
-    <sheet name="skills" sheetId="12" r:id="rId12"/>
+    <sheet name="ERD 다이어그램" sheetId="17" r:id="rId1"/>
+    <sheet name="정수화 정리" sheetId="15" r:id="rId2"/>
+    <sheet name="users" sheetId="6" r:id="rId3"/>
+    <sheet name="items" sheetId="13" r:id="rId4"/>
+    <sheet name="event_list" sheetId="1" r:id="rId5"/>
+    <sheet name="stage_list" sheetId="2" r:id="rId6"/>
+    <sheet name="achievement" sheetId="3" r:id="rId7"/>
+    <sheet name="achievement_reward" sheetId="4" r:id="rId8"/>
+    <sheet name="level_reward" sheetId="5" r:id="rId9"/>
+    <sheet name="special_reward" sheetId="8" r:id="rId10"/>
+    <sheet name="pause_list" sheetId="9" r:id="rId11"/>
+    <sheet name="party" sheetId="10" r:id="rId12"/>
+    <sheet name="bangboo" sheetId="11" r:id="rId13"/>
+    <sheet name="skills" sheetId="12" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,10 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="328">
-  <si>
-    <t>permanent</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="409">
   <si>
     <t>비스트 비트 - 스테이션</t>
   </si>
@@ -72,9 +71,6 @@
   </si>
   <si>
     <t>신입 로프꾼 연습</t>
-  </si>
-  <si>
-    <t>limited</t>
   </si>
   <si>
     <t>비스트 비트 시즌 개막</t>
@@ -317,191 +313,191 @@
   </si>
   <si>
     <t>has_bangboo_1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>has_bangboo_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>has_bangboo_3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>has_bangboo_4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>has_bangboo_5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>has_bangboo_6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>has_bangboo_7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>has_bangboo_8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>has_bangboo_9</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>has_bangboo_10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>has_bangboo_11</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>has_bangboo_12</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>name</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>grade</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>그 화제의 게임, [비스트 비트]가 드디어 뉴에리두에 입성했습니다!
 챔피언전에 참가하려면, 당신만의 파트너가 필요합니다.
 어떤 Bangboo를 선택하시겠습니까?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이벤트 목록 예시 텍스트입니다.
 이벤트 목록 예시 텍스트입니다.
 이벤트 목록 예시 텍스트입니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>벨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>리카온</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>에너지 풀 충전! 재미있어지겠는걸?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>아우</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>빌리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>그레이스</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>npc 대사 예시</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>점장님, 최고의 승부로 보답하겠습니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>s_name</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Random Play!</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>가판대 직원</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>갓핑거</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>벨로보그 중공업</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>교활한 토끼굴</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>세스</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>치안국</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>대공동 6과</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>외환선</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>아스트라</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>스타즈 오브 리라</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>빅토리아 하우스키핑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>버니스</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>오볼로스 소대</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>11호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>운규산</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>괴담방</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>귤복복</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>앨리스</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>AOD</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>수나</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>2;3;9</t>
@@ -540,191 +536,172 @@
     <t>2;3;6500</t>
   </si>
   <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>BRN</t>
-  </si>
-  <si>
-    <t>FRZ</t>
-  </si>
-  <si>
-    <t>PAR</t>
-  </si>
-  <si>
-    <t>CNF</t>
-  </si>
-  <si>
     <t>b2_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>b3_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>응급수리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>s_num</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>b_lv</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>id</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테이지 번호</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>스테이지 이름</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>1번 방부 아이디</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>2번 방부 아이디</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>3번 방부 아이디</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>npc 방부 레벨</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>클리어 레벨업 수치</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>보상 아이디</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>보상량</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>아이디</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>e_name</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>npc_name</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>npc_con</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>npc_type</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>b1_id</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>level_gain</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>reward_ids</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>reward_amounts</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>이벤트 종류</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>category</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>updated_at</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이벤트 이름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>이벤트 설명</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>업적 보상 아이디</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>레벨 보상 아이디</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>title</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>description</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>reward_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>achievement_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>유저 이름</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>한정 보상 획득 여부</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>레벨 보상 획득 여부</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>1번 방부 획득 여부</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>2번 방부 획득 여부</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>3번 방부 획득 여부</t>
@@ -758,39 +735,39 @@
   </si>
   <si>
     <t>is_get_lm_reward</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>is_get_lv_reward</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>bool</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>플레이어1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>플레이어2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>아이템 등급</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>아이템 이름</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>아이템1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>아이템4</t>
@@ -845,281 +822,277 @@
   </si>
   <si>
     <t>아이템2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>아이템3</t>
   </si>
   <si>
     <t>이벤트 아이디</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>등장 npc</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>npc 대사</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>npc 속성</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>name</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>업적 이름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>아이템 아이디</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>items_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>업적 보상 이름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>achievement_info</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>수량</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>amount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>달성 레벨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>lv_num</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>종류</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>type</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>설명 제목</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>정보 이름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>목표 제목</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>목표 내용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>npc 대사</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>설명내용1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>설명내용2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>info1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>info2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>info3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>info4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>info5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>info6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>유저 아이디</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>uid</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>방부 아이디</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>bid</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>출전 중 확인</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>is_on_field</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>bool</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>체력</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>hp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>상태</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>state</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>레벨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>level</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>방부 이름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>속성</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>공격력</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>atk</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>방어력</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>def</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>해금 레벨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>release_lv</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>스킬 이름</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>스킬 위력</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>dmg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>최대 사용량</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>max_num</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>상태이상 여부</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>dbf_type</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>상태이상 확률</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>dbf_ prob</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>업적 아이디</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>a_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>1번 스테이지 클리어 여부</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>2번 스테이지 클리어 여부</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>3번 스테이지 클리어 여부</t>
@@ -1159,7 +1132,7 @@
   </si>
   <si>
     <t>is_st1_clear</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>is_st2_clear</t>
@@ -1199,6 +1172,360 @@
   </si>
   <si>
     <t>is_st14_clear</t>
+  </si>
+  <si>
+    <t>업데이트 날짜</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>이벤트 레벨</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>주인공 성별</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>gender</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 종류</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;3;9</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;5;5000</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;3;9</t>
+  </si>
+  <si>
+    <t>1;5;5000</t>
+  </si>
+  <si>
+    <t>방부 설명</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>info</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>예시 텍스트입니다</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>users</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage_list</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc·방부의 속성</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>남자</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>워밍업</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>여자</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>예선전</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>불</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>본선</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>items</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>grade</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>결승전</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>C급</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>에테르</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>B급</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>special_reward</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>A급</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>업적 보상</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>special</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>상태이상</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>state</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>S급</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨 보상</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxlevel</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>정상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>마비</t>
+  </si>
+  <si>
+    <t>event_list</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼음</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>상시</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>화상</t>
+  </si>
+  <si>
+    <t>한정</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>기절</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>혼란</t>
+  </si>
+  <si>
+    <t>테이블 이름</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>테이블 설명</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용 범위</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>유저 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>유저별 이벤트 진행 정보를 가진 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">아이템 테이블 </t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 내 존재하는 전체 아이템 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>이벤트 목록 테이블</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 내 존재하는 전체 이벤트 목록 정보 테이블</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 목록 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>이벤트별 스테이지 목록 정보 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>achievement</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>업적 보상 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>업적 정보를 가진 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>achievement_rewards</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>업적 보상 아이템 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>업적 별 제공 보상 아이템 목록 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>level_reward</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨 보상 아이템 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨 별 제공 보상 아이템 목록 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>특별 보상 아이템 테이블</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>이벤트에서 제공하는 한정 보상 아이템 테이블</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pause_list</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>일시정지 정보 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>일시정지 팝업창에 출력되는 정보 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>party</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>파티 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>유저가 현재 편성 중인 파티의 정보 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>bangboo</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>방부 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>이벤트 내 존재하는 전체 방부 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>skills</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>이벤트 내 존재하는 전체 방부의 스킬 테이블</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>string형의 실제 처리는 SQL에서 지원하는 varchar()형으로 사용합니다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool형의 실제 처리는 SQL에서 지원하는 tinyint형으로 사용합니다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1208,10 +1535,26 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1263,8 +1606,37 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1306,8 +1678,14 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1343,101 +1721,447 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="4" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="18" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="5">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="3" xr:uid="{5A0F2B00-1513-4B76-87AA-937FAF790C32}"/>
+    <cellStyle name="표준 2 2" xfId="4" xr:uid="{B718E742-F98C-4EAB-AB59-5C117B41C86C}"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1450,6 +2174,60 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>290133</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>50320</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>195036</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE3388A7-21AE-40E5-8ED3-3BFC2261B4B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="290133" y="272570"/>
+          <a:ext cx="5247067" cy="6424866"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1663,503 +2441,732 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:AE5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FC6240E-8987-4B3A-9494-138D3CCA2FFA}">
+  <dimension ref="A1:N32"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="11" width="8.6640625" style="53"/>
+    <col min="12" max="12" width="20.4140625" style="53" customWidth="1"/>
+    <col min="13" max="13" width="25.58203125" style="53" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="42.9140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.6640625" style="53"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="17.5" thickBot="1">
+      <c r="A1" s="50"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="52"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="54"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="56"/>
+      <c r="L2" s="57" t="s">
+        <v>371</v>
+      </c>
+      <c r="M2" s="58" t="s">
+        <v>372</v>
+      </c>
+      <c r="N2" s="59" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="54"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="56"/>
+      <c r="L3" s="60" t="s">
+        <v>334</v>
+      </c>
+      <c r="M3" s="61" t="s">
+        <v>374</v>
+      </c>
+      <c r="N3" s="62" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="54"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="56"/>
+      <c r="L4" s="60" t="s">
+        <v>346</v>
+      </c>
+      <c r="M4" s="61" t="s">
+        <v>376</v>
+      </c>
+      <c r="N4" s="62" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="54"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="56"/>
+      <c r="L5" s="60" t="s">
+        <v>364</v>
+      </c>
+      <c r="M5" s="61" t="s">
+        <v>378</v>
+      </c>
+      <c r="N5" s="62" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="54"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="56"/>
+      <c r="L6" s="60" t="s">
+        <v>336</v>
+      </c>
+      <c r="M6" s="61" t="s">
+        <v>380</v>
+      </c>
+      <c r="N6" s="62" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="54"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="56"/>
+      <c r="L7" s="60" t="s">
+        <v>382</v>
+      </c>
+      <c r="M7" s="61" t="s">
+        <v>383</v>
+      </c>
+      <c r="N7" s="62" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="54"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="56"/>
+      <c r="L8" s="60" t="s">
+        <v>385</v>
+      </c>
+      <c r="M8" s="61" t="s">
+        <v>386</v>
+      </c>
+      <c r="N8" s="63" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="54"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="56"/>
+      <c r="L9" s="60" t="s">
+        <v>388</v>
+      </c>
+      <c r="M9" s="61" t="s">
+        <v>389</v>
+      </c>
+      <c r="N9" s="62" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="54"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="56"/>
+      <c r="L10" s="60" t="s">
+        <v>353</v>
+      </c>
+      <c r="M10" s="61" t="s">
+        <v>391</v>
+      </c>
+      <c r="N10" s="62" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="54"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="56"/>
+      <c r="L11" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="M11" s="61" t="s">
+        <v>394</v>
+      </c>
+      <c r="N11" s="62" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="54"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="56"/>
+      <c r="L12" s="60" t="s">
+        <v>396</v>
+      </c>
+      <c r="M12" s="61" t="s">
+        <v>397</v>
+      </c>
+      <c r="N12" s="62" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="54"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="56"/>
+      <c r="L13" s="60" t="s">
+        <v>399</v>
+      </c>
+      <c r="M13" s="61" t="s">
+        <v>400</v>
+      </c>
+      <c r="N13" s="62" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="17.5" thickBot="1">
+      <c r="A14" s="54"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="56"/>
+      <c r="L14" s="64" t="s">
+        <v>402</v>
+      </c>
+      <c r="M14" s="65" t="s">
+        <v>403</v>
+      </c>
+      <c r="N14" s="66" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="17.5" thickBot="1">
+      <c r="A15" s="54"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="56"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="54"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="56"/>
+      <c r="L16" s="67" t="s">
+        <v>405</v>
+      </c>
+      <c r="M16" s="68"/>
+      <c r="N16" s="69"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="54"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="56"/>
+      <c r="L17" s="70" t="s">
+        <v>406</v>
+      </c>
+      <c r="M17" s="71"/>
+      <c r="N17" s="72"/>
+    </row>
+    <row r="18" spans="1:14" ht="17.5" thickBot="1">
+      <c r="A18" s="54"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="56"/>
+      <c r="L18" s="73" t="s">
+        <v>407</v>
+      </c>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="54"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="56"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="54"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="56"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="54"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="56"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="54"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="56"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="54"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="56"/>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="54"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="56"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="54"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="56"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="54"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="56"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="54"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="56"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="54"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="56"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="54"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="56"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="54"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="56"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="54"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="56"/>
+    </row>
+    <row r="32" spans="1:14" ht="17.5" thickBot="1">
+      <c r="A32" s="76"/>
+      <c r="B32" s="77"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="77"/>
+      <c r="F32" s="77"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="78"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="3" width="22.5" style="1" customWidth="1"/>
-    <col min="4" max="19" width="23.1640625" style="1" customWidth="1"/>
-    <col min="20" max="22" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.9140625" style="1" customWidth="1"/>
-    <col min="25" max="29" width="16.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="17.4140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="20" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="AE1" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31">
+        <v>162</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD2" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE2" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31">
+        <v>151</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="AD3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="AE3" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" ht="20" customHeight="1">
+        <v>152</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="20" customHeight="1">
       <c r="A4" s="6">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>4</v>
+        <v>32</v>
+      </c>
+      <c r="C4" s="6">
+        <v>10</v>
       </c>
       <c r="D4" s="6">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6">
-        <v>0</v>
-      </c>
-      <c r="K4" s="6">
-        <v>0</v>
-      </c>
-      <c r="L4" s="6">
-        <v>0</v>
-      </c>
-      <c r="M4" s="6">
-        <v>0</v>
-      </c>
-      <c r="N4" s="6">
-        <v>0</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6">
-        <v>0</v>
-      </c>
-      <c r="S4" s="6">
-        <v>0</v>
-      </c>
-      <c r="T4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="U4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="W4" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="X4" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" ht="20" customHeight="1">
-      <c r="A5" s="9">
-        <v>2</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C5" s="9">
-        <v>1</v>
-      </c>
-      <c r="D5" s="9">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9">
-        <v>0</v>
-      </c>
-      <c r="G5" s="9">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9">
-        <v>0</v>
-      </c>
-      <c r="I5" s="9">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9">
-        <v>0</v>
-      </c>
-      <c r="K5" s="9">
-        <v>0</v>
-      </c>
-      <c r="L5" s="9">
-        <v>0</v>
-      </c>
-      <c r="M5" s="9">
-        <v>0</v>
-      </c>
-      <c r="N5" s="9">
-        <v>0</v>
-      </c>
-      <c r="O5" s="9">
-        <v>0</v>
-      </c>
-      <c r="P5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>0</v>
-      </c>
-      <c r="R5" s="9">
-        <v>0</v>
-      </c>
-      <c r="S5" s="9">
-        <v>0</v>
-      </c>
-      <c r="T5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="W5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="X5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="20" customHeight="1">
+      <c r="A5" s="25">
+        <v>2</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="25">
+        <v>11</v>
+      </c>
+      <c r="D5" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="20" customHeight="1">
+      <c r="A6" s="6">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="6">
+        <v>12</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="17" style="1" customWidth="1"/>
+    <col min="2" max="6" width="32" style="1" customWidth="1"/>
+    <col min="7" max="8" width="60" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="50" customHeight="1">
+      <c r="A4" s="31">
+        <v>1</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="17"/>
@@ -2171,62 +3178,62 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2290,373 +3297,418 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="9.08203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="22" style="3" customWidth="1"/>
-    <col min="3" max="6" width="16" style="3" customWidth="1"/>
-    <col min="7" max="7" width="18" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="8.6640625" style="3"/>
+    <col min="2" max="3" width="22" style="3" customWidth="1"/>
+    <col min="4" max="7" width="16" style="3" customWidth="1"/>
+    <col min="8" max="8" width="18" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>281</v>
+        <v>329</v>
       </c>
       <c r="D1" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="E1" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>284</v>
-      </c>
       <c r="G1" s="22" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>275</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>252</v>
+        <v>330</v>
       </c>
       <c r="D2" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="F2" s="23" t="s">
         <v>274</v>
       </c>
-      <c r="E2" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>285</v>
-      </c>
       <c r="G2" s="23" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>276</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>242</v>
+        <v>331</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="20" customHeight="1">
+        <v>234</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="20" customHeight="1">
       <c r="A4" s="30">
         <v>1</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="30">
-        <v>1</v>
+        <v>41</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>332</v>
       </c>
       <c r="D4" s="30">
+        <v>1</v>
+      </c>
+      <c r="E4" s="30">
         <v>800</v>
-      </c>
-      <c r="E4" s="30">
-        <v>50</v>
       </c>
       <c r="F4" s="30">
         <v>50</v>
       </c>
       <c r="G4" s="30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="20" customHeight="1">
+        <v>50</v>
+      </c>
+      <c r="H4" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20" customHeight="1">
       <c r="A5" s="29">
         <v>2</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="29">
-        <v>2</v>
+        <v>42</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>332</v>
       </c>
       <c r="D5" s="29">
+        <v>2</v>
+      </c>
+      <c r="E5" s="29">
         <v>750</v>
       </c>
-      <c r="E5" s="29">
+      <c r="F5" s="29">
         <v>60</v>
       </c>
-      <c r="F5" s="29">
+      <c r="G5" s="29">
         <v>50</v>
       </c>
-      <c r="G5" s="29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="20" customHeight="1">
+      <c r="H5" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20" customHeight="1">
       <c r="A6" s="30">
         <v>3</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="30">
+        <v>43</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="D6" s="30">
         <v>3</v>
       </c>
-      <c r="D6" s="30">
+      <c r="E6" s="30">
         <v>600</v>
       </c>
-      <c r="E6" s="30">
+      <c r="F6" s="30">
         <v>90</v>
       </c>
-      <c r="F6" s="30">
+      <c r="G6" s="30">
         <v>60</v>
       </c>
-      <c r="G6" s="30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="20" customHeight="1">
+      <c r="H6" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20" customHeight="1">
       <c r="A7" s="32">
         <v>4</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="32">
+        <v>44</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="D7" s="32">
         <v>4</v>
       </c>
-      <c r="D7" s="32">
+      <c r="E7" s="32">
         <v>620</v>
       </c>
-      <c r="E7" s="32">
+      <c r="F7" s="32">
         <v>85</v>
       </c>
-      <c r="F7" s="32">
+      <c r="G7" s="32">
         <v>40</v>
       </c>
-      <c r="G7" s="32">
+      <c r="H7" s="32">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="20" customHeight="1">
+    <row r="8" spans="1:8" ht="20" customHeight="1">
       <c r="A8" s="33">
         <v>5</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="33">
-        <v>1</v>
+        <v>45</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>332</v>
       </c>
       <c r="D8" s="33">
+        <v>1</v>
+      </c>
+      <c r="E8" s="33">
         <v>840</v>
       </c>
-      <c r="E8" s="33">
+      <c r="F8" s="33">
         <v>58</v>
       </c>
-      <c r="F8" s="33">
+      <c r="G8" s="33">
         <v>62</v>
       </c>
-      <c r="G8" s="33">
+      <c r="H8" s="33">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="20" customHeight="1">
+    <row r="9" spans="1:8" ht="20" customHeight="1">
       <c r="A9" s="32">
         <v>6</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="32">
+        <v>46</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="D9" s="32">
         <v>5</v>
       </c>
-      <c r="D9" s="32">
+      <c r="E9" s="32">
         <v>700</v>
       </c>
-      <c r="E9" s="32">
+      <c r="F9" s="32">
         <v>78</v>
       </c>
-      <c r="F9" s="32">
+      <c r="G9" s="32">
         <v>50</v>
       </c>
-      <c r="G9" s="32">
+      <c r="H9" s="32">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="20" customHeight="1">
+    <row r="10" spans="1:8" ht="20" customHeight="1">
       <c r="A10" s="33">
         <v>7</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="33">
-        <v>2</v>
+        <v>47</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>332</v>
       </c>
       <c r="D10" s="33">
+        <v>2</v>
+      </c>
+      <c r="E10" s="33">
         <v>690</v>
       </c>
-      <c r="E10" s="33">
+      <c r="F10" s="33">
         <v>88</v>
       </c>
-      <c r="F10" s="33">
+      <c r="G10" s="33">
         <v>42</v>
       </c>
-      <c r="G10" s="33">
+      <c r="H10" s="33">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="20" customHeight="1">
+    <row r="11" spans="1:8" ht="20" customHeight="1">
       <c r="A11" s="32">
         <v>8</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="32">
+        <v>48</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="D11" s="32">
         <v>3</v>
       </c>
-      <c r="D11" s="32">
+      <c r="E11" s="32">
         <v>880</v>
       </c>
-      <c r="E11" s="32">
+      <c r="F11" s="32">
         <v>60</v>
       </c>
-      <c r="F11" s="32">
+      <c r="G11" s="32">
         <v>78</v>
       </c>
-      <c r="G11" s="32">
+      <c r="H11" s="32">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="20" customHeight="1">
+    <row r="12" spans="1:8" ht="20" customHeight="1">
       <c r="A12" s="33">
         <v>9</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="33">
+        <v>49</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="D12" s="33">
         <v>4</v>
       </c>
-      <c r="D12" s="33">
+      <c r="E12" s="33">
         <v>660</v>
       </c>
-      <c r="E12" s="33">
+      <c r="F12" s="33">
         <v>95</v>
       </c>
-      <c r="F12" s="33">
+      <c r="G12" s="33">
         <v>45</v>
       </c>
-      <c r="G12" s="33">
+      <c r="H12" s="33">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="20" customHeight="1">
+    <row r="13" spans="1:8" ht="20" customHeight="1">
       <c r="A13" s="32">
         <v>10</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="32">
+        <v>50</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="D13" s="32">
         <v>5</v>
       </c>
-      <c r="D13" s="32">
+      <c r="E13" s="32">
         <v>760</v>
       </c>
-      <c r="E13" s="32">
+      <c r="F13" s="32">
         <v>85</v>
       </c>
-      <c r="F13" s="32">
+      <c r="G13" s="32">
         <v>58</v>
       </c>
-      <c r="G13" s="32">
+      <c r="H13" s="32">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="20" customHeight="1">
+    <row r="14" spans="1:8" ht="20" customHeight="1">
       <c r="A14" s="33">
         <v>11</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="33">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>332</v>
       </c>
       <c r="D14" s="33">
+        <v>1</v>
+      </c>
+      <c r="E14" s="33">
         <v>960</v>
       </c>
-      <c r="E14" s="33">
+      <c r="F14" s="33">
         <v>70</v>
       </c>
-      <c r="F14" s="33">
+      <c r="G14" s="33">
         <v>82</v>
       </c>
-      <c r="G14" s="33">
+      <c r="H14" s="33">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="20" customHeight="1">
+    <row r="15" spans="1:8" ht="20" customHeight="1">
       <c r="A15" s="32">
         <v>12</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="32">
+        <v>52</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="D15" s="32">
         <v>5</v>
       </c>
-      <c r="D15" s="32">
+      <c r="E15" s="32">
         <v>820</v>
       </c>
-      <c r="E15" s="32">
+      <c r="F15" s="32">
         <v>95</v>
       </c>
-      <c r="F15" s="32">
+      <c r="G15" s="32">
         <v>65</v>
       </c>
-      <c r="G15" s="32">
+      <c r="H15" s="32">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="13.4" customHeight="1"/>
+    <row r="16" spans="1:8" ht="13.4" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="whole" sqref="G4:G15" xr:uid="{00000000-0002-0000-0900-000000000000}">
+  <phoneticPr fontId="4" type="noConversion"/>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="whole" sqref="H4:H15" xr:uid="{00000000-0002-0000-0900-000000000000}">
       <formula1>1</formula1>
       <formula2>20</formula2>
     </dataValidation>
@@ -2665,7 +3717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="17"/>
@@ -2682,80 +3734,80 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>241</v>
+        <v>333</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20" customHeight="1">
@@ -2766,7 +3818,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D4" s="7">
         <v>230</v>
@@ -2777,8 +3829,8 @@
       <c r="F4" s="7">
         <v>15</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>148</v>
+      <c r="G4" s="8">
+        <v>1</v>
       </c>
       <c r="H4" s="8">
         <v>0</v>
@@ -2792,7 +3844,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D5" s="26">
         <v>320</v>
@@ -2803,8 +3855,8 @@
       <c r="F5" s="26">
         <v>10</v>
       </c>
-      <c r="G5" s="34" t="s">
-        <v>148</v>
+      <c r="G5" s="34">
+        <v>1</v>
       </c>
       <c r="H5" s="34">
         <v>0</v>
@@ -2818,7 +3870,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D6" s="7">
         <v>250</v>
@@ -2829,8 +3881,8 @@
       <c r="F6" s="7">
         <v>5</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>148</v>
+      <c r="G6" s="8">
+        <v>1</v>
       </c>
       <c r="H6" s="8">
         <v>0</v>
@@ -2844,7 +3896,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D7" s="26">
         <v>230</v>
@@ -2855,8 +3907,8 @@
       <c r="F7" s="26">
         <v>20</v>
       </c>
-      <c r="G7" s="34" t="s">
-        <v>148</v>
+      <c r="G7" s="34">
+        <v>1</v>
       </c>
       <c r="H7" s="34">
         <v>0</v>
@@ -2870,7 +3922,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D8" s="7">
         <v>330</v>
@@ -2881,8 +3933,8 @@
       <c r="F8" s="7">
         <v>10</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>148</v>
+      <c r="G8" s="8">
+        <v>1</v>
       </c>
       <c r="H8" s="8">
         <v>0</v>
@@ -2896,7 +3948,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" s="26">
         <v>250</v>
@@ -2907,8 +3959,8 @@
       <c r="F9" s="26">
         <v>5</v>
       </c>
-      <c r="G9" s="34" t="s">
-        <v>149</v>
+      <c r="G9" s="34">
+        <v>4</v>
       </c>
       <c r="H9" s="34">
         <v>30</v>
@@ -2922,7 +3974,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D10" s="7">
         <v>230</v>
@@ -2933,8 +3985,8 @@
       <c r="F10" s="7">
         <v>18</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>148</v>
+      <c r="G10" s="8">
+        <v>1</v>
       </c>
       <c r="H10" s="8">
         <v>0</v>
@@ -2948,7 +4000,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D11" s="26">
         <v>350</v>
@@ -2959,8 +4011,8 @@
       <c r="F11" s="26">
         <v>10</v>
       </c>
-      <c r="G11" s="34" t="s">
-        <v>148</v>
+      <c r="G11" s="34">
+        <v>1</v>
       </c>
       <c r="H11" s="34">
         <v>0</v>
@@ -2974,7 +4026,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D12" s="7">
         <v>250</v>
@@ -2985,8 +4037,8 @@
       <c r="F12" s="7">
         <v>5</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>150</v>
+      <c r="G12" s="8">
+        <v>3</v>
       </c>
       <c r="H12" s="8">
         <v>25</v>
@@ -3000,7 +4052,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13" s="34">
         <v>230</v>
@@ -3011,8 +4063,8 @@
       <c r="F13" s="34">
         <v>20</v>
       </c>
-      <c r="G13" s="34" t="s">
-        <v>148</v>
+      <c r="G13" s="34">
+        <v>1</v>
       </c>
       <c r="H13" s="34">
         <v>0</v>
@@ -3026,7 +4078,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" s="8">
         <v>310</v>
@@ -3037,8 +4089,8 @@
       <c r="F14" s="8">
         <v>10</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>151</v>
+      <c r="G14" s="8">
+        <v>2</v>
       </c>
       <c r="H14" s="8">
         <v>20</v>
@@ -3052,7 +4104,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" s="34">
         <v>250</v>
@@ -3063,8 +4115,8 @@
       <c r="F15" s="34">
         <v>5</v>
       </c>
-      <c r="G15" s="34" t="s">
-        <v>151</v>
+      <c r="G15" s="34">
+        <v>2</v>
       </c>
       <c r="H15" s="34">
         <v>40</v>
@@ -3078,7 +4130,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D16" s="8">
         <v>230</v>
@@ -3089,8 +4141,8 @@
       <c r="F16" s="8">
         <v>18</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>148</v>
+      <c r="G16" s="8">
+        <v>1</v>
       </c>
       <c r="H16" s="8">
         <v>0</v>
@@ -3104,7 +4156,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D17" s="34">
         <v>320</v>
@@ -3115,8 +4167,8 @@
       <c r="F17" s="34">
         <v>10</v>
       </c>
-      <c r="G17" s="34" t="s">
-        <v>148</v>
+      <c r="G17" s="34">
+        <v>1</v>
       </c>
       <c r="H17" s="34">
         <v>0</v>
@@ -3130,7 +4182,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D18" s="8">
         <v>250</v>
@@ -3141,8 +4193,8 @@
       <c r="F18" s="8">
         <v>5</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>148</v>
+      <c r="G18" s="8">
+        <v>1</v>
       </c>
       <c r="H18" s="8">
         <v>0</v>
@@ -3156,7 +4208,7 @@
         <v>6</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D19" s="34">
         <v>230</v>
@@ -3167,8 +4219,8 @@
       <c r="F19" s="34">
         <v>18</v>
       </c>
-      <c r="G19" s="34" t="s">
-        <v>148</v>
+      <c r="G19" s="34">
+        <v>1</v>
       </c>
       <c r="H19" s="34">
         <v>0</v>
@@ -3182,7 +4234,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D20" s="8">
         <v>340</v>
@@ -3193,8 +4245,8 @@
       <c r="F20" s="8">
         <v>12</v>
       </c>
-      <c r="G20" s="8" t="s">
-        <v>148</v>
+      <c r="G20" s="8">
+        <v>1</v>
       </c>
       <c r="H20" s="8">
         <v>0</v>
@@ -3208,7 +4260,7 @@
         <v>6</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D21" s="34">
         <v>250</v>
@@ -3219,8 +4271,8 @@
       <c r="F21" s="34">
         <v>5</v>
       </c>
-      <c r="G21" s="34" t="s">
-        <v>152</v>
+      <c r="G21" s="34">
+        <v>6</v>
       </c>
       <c r="H21" s="34">
         <v>35</v>
@@ -3234,7 +4286,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D22" s="8">
         <v>230</v>
@@ -3245,8 +4297,8 @@
       <c r="F22" s="8">
         <v>18</v>
       </c>
-      <c r="G22" s="8" t="s">
-        <v>148</v>
+      <c r="G22" s="8">
+        <v>1</v>
       </c>
       <c r="H22" s="8">
         <v>0</v>
@@ -3260,7 +4312,7 @@
         <v>7</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D23" s="34">
         <v>310</v>
@@ -3271,8 +4323,8 @@
       <c r="F23" s="34">
         <v>10</v>
       </c>
-      <c r="G23" s="34" t="s">
-        <v>149</v>
+      <c r="G23" s="34">
+        <v>4</v>
       </c>
       <c r="H23" s="34">
         <v>20</v>
@@ -3286,7 +4338,7 @@
         <v>7</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D24" s="8">
         <v>250</v>
@@ -3297,8 +4349,8 @@
       <c r="F24" s="8">
         <v>5</v>
       </c>
-      <c r="G24" s="8" t="s">
-        <v>149</v>
+      <c r="G24" s="8">
+        <v>4</v>
       </c>
       <c r="H24" s="8">
         <v>45</v>
@@ -3312,7 +4364,7 @@
         <v>8</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D25" s="34">
         <v>230</v>
@@ -3323,8 +4375,8 @@
       <c r="F25" s="34">
         <v>18</v>
       </c>
-      <c r="G25" s="34" t="s">
-        <v>148</v>
+      <c r="G25" s="34">
+        <v>1</v>
       </c>
       <c r="H25" s="34">
         <v>0</v>
@@ -3338,7 +4390,7 @@
         <v>8</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D26" s="8">
         <v>320</v>
@@ -3349,8 +4401,8 @@
       <c r="F26" s="8">
         <v>10</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>150</v>
+      <c r="G26" s="8">
+        <v>3</v>
       </c>
       <c r="H26" s="8">
         <v>15</v>
@@ -3364,7 +4416,7 @@
         <v>8</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D27" s="34">
         <v>250</v>
@@ -3375,8 +4427,8 @@
       <c r="F27" s="34">
         <v>5</v>
       </c>
-      <c r="G27" s="34" t="s">
-        <v>150</v>
+      <c r="G27" s="34">
+        <v>3</v>
       </c>
       <c r="H27" s="34">
         <v>30</v>
@@ -3390,7 +4442,7 @@
         <v>9</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D28" s="8">
         <v>230</v>
@@ -3401,8 +4453,8 @@
       <c r="F28" s="8">
         <v>20</v>
       </c>
-      <c r="G28" s="8" t="s">
-        <v>148</v>
+      <c r="G28" s="8">
+        <v>1</v>
       </c>
       <c r="H28" s="8">
         <v>0</v>
@@ -3416,7 +4468,7 @@
         <v>9</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D29" s="34">
         <v>350</v>
@@ -3427,8 +4479,8 @@
       <c r="F29" s="34">
         <v>12</v>
       </c>
-      <c r="G29" s="34" t="s">
-        <v>148</v>
+      <c r="G29" s="34">
+        <v>1</v>
       </c>
       <c r="H29" s="34">
         <v>0</v>
@@ -3442,7 +4494,7 @@
         <v>9</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D30" s="8">
         <v>250</v>
@@ -3453,8 +4505,8 @@
       <c r="F30" s="8">
         <v>5</v>
       </c>
-      <c r="G30" s="8" t="s">
-        <v>151</v>
+      <c r="G30" s="8">
+        <v>2</v>
       </c>
       <c r="H30" s="8">
         <v>35</v>
@@ -3468,7 +4520,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D31" s="34">
         <v>230</v>
@@ -3479,8 +4531,8 @@
       <c r="F31" s="34">
         <v>18</v>
       </c>
-      <c r="G31" s="34" t="s">
-        <v>148</v>
+      <c r="G31" s="34">
+        <v>1</v>
       </c>
       <c r="H31" s="34">
         <v>0</v>
@@ -3494,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D32" s="8">
         <v>320</v>
@@ -3505,8 +4557,8 @@
       <c r="F32" s="8">
         <v>12</v>
       </c>
-      <c r="G32" s="8" t="s">
-        <v>152</v>
+      <c r="G32" s="8">
+        <v>6</v>
       </c>
       <c r="H32" s="8">
         <v>15</v>
@@ -3520,7 +4572,7 @@
         <v>10</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D33" s="34">
         <v>250</v>
@@ -3531,8 +4583,8 @@
       <c r="F33" s="34">
         <v>5</v>
       </c>
-      <c r="G33" s="34" t="s">
-        <v>152</v>
+      <c r="G33" s="34">
+        <v>6</v>
       </c>
       <c r="H33" s="34">
         <v>30</v>
@@ -3546,7 +4598,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D34" s="8">
         <v>230</v>
@@ -3557,8 +4609,8 @@
       <c r="F34" s="8">
         <v>18</v>
       </c>
-      <c r="G34" s="8" t="s">
-        <v>148</v>
+      <c r="G34" s="8">
+        <v>1</v>
       </c>
       <c r="H34" s="8">
         <v>0</v>
@@ -3572,7 +4624,7 @@
         <v>11</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D35" s="34">
         <v>330</v>
@@ -3583,8 +4635,8 @@
       <c r="F35" s="34">
         <v>10</v>
       </c>
-      <c r="G35" s="34" t="s">
-        <v>148</v>
+      <c r="G35" s="34">
+        <v>1</v>
       </c>
       <c r="H35" s="34">
         <v>0</v>
@@ -3598,7 +4650,7 @@
         <v>11</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D36" s="8">
         <v>250</v>
@@ -3609,8 +4661,8 @@
       <c r="F36" s="8">
         <v>5</v>
       </c>
-      <c r="G36" s="8" t="s">
-        <v>148</v>
+      <c r="G36" s="8">
+        <v>1</v>
       </c>
       <c r="H36" s="8">
         <v>0</v>
@@ -3624,7 +4676,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D37" s="34">
         <v>230</v>
@@ -3635,8 +4687,8 @@
       <c r="F37" s="34">
         <v>20</v>
       </c>
-      <c r="G37" s="34" t="s">
-        <v>148</v>
+      <c r="G37" s="34">
+        <v>1</v>
       </c>
       <c r="H37" s="34">
         <v>0</v>
@@ -3650,7 +4702,7 @@
         <v>12</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D38" s="8">
         <v>350</v>
@@ -3661,8 +4713,8 @@
       <c r="F38" s="8">
         <v>12</v>
       </c>
-      <c r="G38" s="8" t="s">
-        <v>148</v>
+      <c r="G38" s="8">
+        <v>1</v>
       </c>
       <c r="H38" s="8">
         <v>0</v>
@@ -3676,7 +4728,7 @@
         <v>12</v>
       </c>
       <c r="C39" s="34" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D39" s="34">
         <v>250</v>
@@ -3687,20 +4739,793 @@
       <c r="F39" s="34">
         <v>5</v>
       </c>
-      <c r="G39" s="34" t="s">
-        <v>152</v>
+      <c r="G39" s="34">
+        <v>6</v>
       </c>
       <c r="H39" s="34">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{197909A6-F373-438F-BCBC-FC540F2710CA}">
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="3" width="8.6640625" style="1"/>
+    <col min="4" max="4" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.6640625" style="1"/>
+    <col min="7" max="7" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="35" t="s">
+        <v>334</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="E1" s="38" t="s">
+        <v>335</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="H1" s="38" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="B2" s="41">
+        <v>1</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>339</v>
+      </c>
+      <c r="E2" s="41">
+        <v>1</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>340</v>
+      </c>
+      <c r="H2" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="17.5" thickBot="1">
+      <c r="A3" s="42" t="s">
+        <v>341</v>
+      </c>
+      <c r="B3" s="43">
+        <v>2</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>342</v>
+      </c>
+      <c r="E3" s="41">
+        <v>2</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="H3" s="41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="17.5" thickBot="1">
+      <c r="D4" s="40" t="s">
+        <v>344</v>
+      </c>
+      <c r="E4" s="41">
+        <v>3</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="H4" s="41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="17.5" thickBot="1">
+      <c r="A5" s="37" t="s">
+        <v>346</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>347</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>348</v>
+      </c>
+      <c r="E5" s="43">
+        <v>4</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>349</v>
+      </c>
+      <c r="H5" s="41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="17.5" thickBot="1">
+      <c r="A6" s="40" t="s">
+        <v>350</v>
+      </c>
+      <c r="B6" s="41">
+        <v>1</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>351</v>
+      </c>
+      <c r="H6" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="17.5" thickBot="1">
+      <c r="A7" s="40" t="s">
+        <v>352</v>
+      </c>
+      <c r="B7" s="41">
+        <v>2</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>353</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="44" t="s">
+        <v>354</v>
+      </c>
+      <c r="B8" s="45">
+        <v>3</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>355</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>356</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>357</v>
+      </c>
+      <c r="H8" s="38" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="17.5" thickBot="1">
+      <c r="A9" s="46" t="s">
+        <v>359</v>
+      </c>
+      <c r="B9" s="47">
+        <v>4</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>360</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>361</v>
+      </c>
+      <c r="G9" s="79" t="s">
+        <v>362</v>
+      </c>
+      <c r="H9" s="80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="17.5" thickBot="1">
+      <c r="G10" s="79" t="s">
+        <v>363</v>
+      </c>
+      <c r="H10" s="80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="37" t="s">
+        <v>364</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="G11" s="79" t="s">
+        <v>365</v>
+      </c>
+      <c r="H11" s="80">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="40" t="s">
+        <v>366</v>
+      </c>
+      <c r="B12" s="41">
+        <v>0</v>
+      </c>
+      <c r="G12" s="79" t="s">
+        <v>367</v>
+      </c>
+      <c r="H12" s="80">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="17.5" thickBot="1">
+      <c r="A13" s="42" t="s">
+        <v>368</v>
+      </c>
+      <c r="B13" s="43">
+        <v>1</v>
+      </c>
+      <c r="G13" s="79" t="s">
+        <v>369</v>
+      </c>
+      <c r="H13" s="80">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="17.5" thickBot="1">
+      <c r="G14" s="81" t="s">
+        <v>370</v>
+      </c>
+      <c r="H14" s="82">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="G15" s="48"/>
+      <c r="H15" s="49"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="G16" s="48"/>
+      <c r="H16" s="49"/>
+    </row>
+    <row r="17" spans="7:8">
+      <c r="G17" s="48"/>
+      <c r="H17" s="49"/>
+    </row>
+    <row r="18" spans="7:8">
+      <c r="G18" s="48"/>
+      <c r="H18" s="49"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="users!A1" display="users" xr:uid="{147AF0B8-F8C0-4D42-99B9-47C0E495828B}"/>
+    <hyperlink ref="D1" location="stage_list!A1" display="stage_list" xr:uid="{3E564BF6-08DE-4595-84A0-9327A975D7A9}"/>
+    <hyperlink ref="A5" location="items!A1" display="items" xr:uid="{022AD69C-B0EB-4359-945F-0C1368043DB9}"/>
+    <hyperlink ref="A11" location="stage_list!A1" display="stage_list" xr:uid="{1CA3FC33-C82F-49FF-B87B-90688D43EE99}"/>
+    <hyperlink ref="D7" location="special_reward!A1" display="special_reward" xr:uid="{0D985F60-6729-4D4F-9998-D715F7D9CF0F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:AF5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="4" width="22.5" style="1" customWidth="1"/>
+    <col min="5" max="20" width="23.1640625" style="1" customWidth="1"/>
+    <col min="21" max="23" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.9140625" style="1" customWidth="1"/>
+    <col min="26" max="30" width="16.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="17.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32">
+      <c r="A1" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
+      <c r="A2" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF2" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
+      <c r="A3" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="AC3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="AD3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="AE3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="AF3" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="20" customHeight="1">
+      <c r="A4" s="6">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" s="6">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0</v>
+      </c>
+      <c r="L4" s="6">
+        <v>0</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6">
+        <v>0</v>
+      </c>
+      <c r="T4" s="6">
+        <v>0</v>
+      </c>
+      <c r="U4" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="V4" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="20" customHeight="1">
+      <c r="A5" s="9">
+        <v>2</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="9">
+        <v>2</v>
+      </c>
+      <c r="D5" s="9">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9">
+        <v>0</v>
+      </c>
+      <c r="L5" s="9">
+        <v>0</v>
+      </c>
+      <c r="M5" s="9">
+        <v>0</v>
+      </c>
+      <c r="N5" s="9">
+        <v>0</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0</v>
+      </c>
+      <c r="P5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0</v>
+      </c>
+      <c r="R5" s="9">
+        <v>0</v>
+      </c>
+      <c r="S5" s="9">
+        <v>0</v>
+      </c>
+      <c r="T5" s="9">
+        <v>0</v>
+      </c>
+      <c r="U5" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{409A23C5-B8CA-44B9-BE71-CBCAADB2D68E}">
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="17"/>
@@ -3713,35 +5538,35 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20" customHeight="1">
@@ -3749,7 +5574,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C4" s="10">
         <v>1</v>
@@ -3760,7 +5585,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C5" s="10">
         <v>2</v>
@@ -3771,7 +5596,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C6" s="10">
         <v>3</v>
@@ -3782,7 +5607,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C7" s="10">
         <v>4</v>
@@ -3793,7 +5618,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C8" s="10">
         <v>1</v>
@@ -3804,7 +5629,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C9" s="10">
         <v>2</v>
@@ -3815,7 +5640,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C10" s="10">
         <v>3</v>
@@ -3826,7 +5651,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C11" s="10">
         <v>4</v>
@@ -3837,7 +5662,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C12" s="10">
         <v>1</v>
@@ -3848,7 +5673,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C13" s="10">
         <v>2</v>
@@ -3859,7 +5684,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C14" s="10">
         <v>3</v>
@@ -3870,7 +5695,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C15" s="10">
         <v>4</v>
@@ -3881,7 +5706,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C16" s="10">
         <v>1</v>
@@ -3892,7 +5717,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C17" s="10">
         <v>2</v>
@@ -3903,7 +5728,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C18" s="10">
         <v>3</v>
@@ -3914,7 +5739,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C19" s="10">
         <v>4</v>
@@ -3925,7 +5750,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C20" s="10">
         <v>1</v>
@@ -3936,7 +5761,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C21" s="10">
         <v>2</v>
@@ -3947,7 +5772,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C22" s="10">
         <v>3</v>
@@ -3958,19 +5783,19 @@
         <v>20</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C23" s="10">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="17"/>
@@ -3986,310 +5811,310 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>161</v>
+        <v>319</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="58" customHeight="1">
       <c r="A4" s="11">
         <v>1</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="12">
         <v>0</v>
       </c>
       <c r="C4" s="13">
         <v>46266</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>104</v>
+      <c r="D4" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>103</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="58" customHeight="1">
       <c r="A5" s="14">
         <v>2</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="15">
         <v>0</v>
       </c>
       <c r="C5" s="16">
         <v>46267</v>
       </c>
       <c r="D5" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="F5" s="15" t="s">
+      <c r="G5" s="15" t="s">
         <v>5</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="58" customHeight="1">
       <c r="A6" s="11">
         <v>3</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="12">
         <v>0</v>
       </c>
       <c r="C6" s="13">
         <v>46268</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="58" customHeight="1">
       <c r="A7" s="14">
         <v>4</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="15">
         <v>0</v>
       </c>
       <c r="C7" s="16">
         <v>46269</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F7" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="15" t="s">
         <v>5</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="58" customHeight="1">
       <c r="A8" s="11">
         <v>5</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="12">
         <v>0</v>
       </c>
       <c r="C8" s="13">
         <v>46270</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="58" customHeight="1">
       <c r="A9" s="17">
         <v>101</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>10</v>
+      <c r="B9" s="18">
+        <v>1</v>
       </c>
       <c r="C9" s="19">
         <v>46266</v>
       </c>
-      <c r="D9" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>105</v>
+      <c r="D9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>102</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="58" customHeight="1">
       <c r="A10" s="14">
         <v>102</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>10</v>
+      <c r="B10" s="15">
+        <v>1</v>
       </c>
       <c r="C10" s="16">
         <v>46267</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F10" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="15" t="s">
         <v>5</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="58" customHeight="1">
       <c r="A11" s="17">
         <v>103</v>
       </c>
-      <c r="B11" s="18" t="s">
-        <v>10</v>
+      <c r="B11" s="18">
+        <v>1</v>
       </c>
       <c r="C11" s="19">
         <v>46268</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="58" customHeight="1">
       <c r="A12" s="14">
         <v>104</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>10</v>
+      <c r="B12" s="15">
+        <v>1</v>
       </c>
       <c r="C12" s="16">
         <v>46269</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F12" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="15" t="s">
         <v>5</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="58" customHeight="1">
       <c r="A13" s="17">
         <v>105</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>10</v>
+      <c r="B13" s="18">
+        <v>1</v>
       </c>
       <c r="C13" s="19">
         <v>46270</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="17"/>
@@ -4310,134 +6135,134 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="I3" s="5">
         <v>1</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="20" customHeight="1">
@@ -4451,14 +6276,14 @@
         <v>1</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E4" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="F4" s="21" t="s">
-        <v>108</v>
-      </c>
       <c r="G4" s="20">
         <v>2</v>
       </c>
@@ -4478,10 +6303,10 @@
         <v>1</v>
       </c>
       <c r="M4" s="20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N4" s="20" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20" customHeight="1">
@@ -4495,13 +6320,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G5" s="14">
         <v>1</v>
@@ -4522,10 +6347,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="N5" s="14" t="s">
         <v>136</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="20" customHeight="1">
@@ -4539,13 +6364,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G6" s="17">
         <v>2</v>
@@ -4566,10 +6391,10 @@
         <v>1</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N6" s="17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="20" customHeight="1">
@@ -4583,13 +6408,13 @@
         <v>1</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G7" s="14">
         <v>4</v>
@@ -4610,10 +6435,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="20" customHeight="1">
@@ -4627,13 +6452,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E8" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>110</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>112</v>
       </c>
       <c r="G8" s="17">
         <v>5</v>
@@ -4654,10 +6479,10 @@
         <v>1</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="20" customHeight="1">
@@ -4671,13 +6496,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G9" s="14">
         <v>3</v>
@@ -4698,10 +6523,10 @@
         <v>2</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="20" customHeight="1">
@@ -4715,13 +6540,13 @@
         <v>2</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G10" s="17">
         <v>3</v>
@@ -4742,10 +6567,10 @@
         <v>2</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="20" customHeight="1">
@@ -4759,13 +6584,13 @@
         <v>2</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G11" s="14">
         <v>5</v>
@@ -4786,10 +6611,10 @@
         <v>3</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="20" customHeight="1">
@@ -4803,13 +6628,13 @@
         <v>2</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G12" s="17">
         <v>1</v>
@@ -4830,10 +6655,10 @@
         <v>3</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="20" customHeight="1">
@@ -4847,13 +6672,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G13" s="14">
         <v>4</v>
@@ -4874,10 +6699,10 @@
         <v>2</v>
       </c>
       <c r="M13" s="14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="20" customHeight="1">
@@ -4891,13 +6716,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G14" s="17">
         <v>3</v>
@@ -4918,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="20" customHeight="1">
@@ -4935,13 +6760,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E15" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E15" s="18" t="s">
-        <v>132</v>
-      </c>
       <c r="F15" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G15" s="17">
         <v>3</v>
@@ -4962,10 +6787,10 @@
         <v>0</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="20" customHeight="1">
@@ -4979,13 +6804,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E16" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>133</v>
-      </c>
       <c r="F16" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G16" s="17">
         <v>3</v>
@@ -5006,10 +6831,10 @@
         <v>0</v>
       </c>
       <c r="M16" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="20" customHeight="1">
@@ -5023,13 +6848,13 @@
         <v>4</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G17" s="11">
         <v>3</v>
@@ -5050,19 +6875,19 @@
         <v>0</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="17"/>
@@ -5074,26 +6899,26 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="20" customHeight="1">
@@ -5101,7 +6926,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="20" customHeight="1">
@@ -5109,7 +6934,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="20" customHeight="1">
@@ -5117,7 +6942,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="20" customHeight="1">
@@ -5125,7 +6950,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="20" customHeight="1">
@@ -5133,7 +6958,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="20" customHeight="1">
@@ -5141,7 +6966,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="20" customHeight="1">
@@ -5149,7 +6974,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="20" customHeight="1">
@@ -5157,16 +6982,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="17"/>
@@ -5181,470 +7006,470 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>242</v>
+        <v>182</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>242</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20" customHeight="1">
       <c r="A4" s="6">
         <v>1</v>
       </c>
-      <c r="B4" s="6">
-        <v>1</v>
+      <c r="B4" s="6" t="s">
+        <v>325</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" s="6">
         <v>1</v>
       </c>
-      <c r="E4" s="6">
-        <v>1</v>
+      <c r="E4" s="6" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20" customHeight="1">
       <c r="A5" s="25">
         <v>2</v>
       </c>
-      <c r="B5" s="25">
-        <v>3</v>
+      <c r="B5" s="6" t="s">
+        <v>325</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" s="25">
         <v>1</v>
       </c>
-      <c r="E5" s="25">
-        <v>5</v>
+      <c r="E5" s="6" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20" customHeight="1">
       <c r="A6" s="6">
         <v>3</v>
       </c>
-      <c r="B6" s="6">
-        <v>9</v>
+      <c r="B6" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
       </c>
-      <c r="E6" s="6">
-        <v>5000</v>
+      <c r="E6" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20" customHeight="1">
       <c r="A7" s="25">
         <v>4</v>
       </c>
-      <c r="B7" s="25">
-        <v>1</v>
+      <c r="B7" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D7" s="25">
         <v>2</v>
       </c>
-      <c r="E7" s="25">
-        <v>1</v>
+      <c r="E7" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20" customHeight="1">
       <c r="A8" s="6">
         <v>5</v>
       </c>
-      <c r="B8" s="6">
-        <v>3</v>
+      <c r="B8" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D8" s="6">
         <v>2</v>
       </c>
-      <c r="E8" s="6">
-        <v>5</v>
+      <c r="E8" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="20" customHeight="1">
       <c r="A9" s="25">
         <v>6</v>
       </c>
-      <c r="B9" s="25">
-        <v>9</v>
+      <c r="B9" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D9" s="25">
         <v>2</v>
       </c>
-      <c r="E9" s="25">
-        <v>5000</v>
+      <c r="E9" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20" customHeight="1">
       <c r="A10" s="6">
         <v>7</v>
       </c>
-      <c r="B10" s="6">
-        <v>1</v>
+      <c r="B10" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" s="6">
         <v>3</v>
       </c>
-      <c r="E10" s="6">
-        <v>1</v>
+      <c r="E10" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="20" customHeight="1">
       <c r="A11" s="25">
         <v>8</v>
       </c>
-      <c r="B11" s="25">
-        <v>3</v>
+      <c r="B11" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D11" s="25">
         <v>3</v>
       </c>
-      <c r="E11" s="25">
-        <v>5</v>
+      <c r="E11" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20" customHeight="1">
       <c r="A12" s="6">
         <v>9</v>
       </c>
-      <c r="B12" s="6">
-        <v>9</v>
+      <c r="B12" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D12" s="6">
         <v>3</v>
       </c>
-      <c r="E12" s="6">
-        <v>5000</v>
+      <c r="E12" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="20" customHeight="1">
       <c r="A13" s="25">
         <v>10</v>
       </c>
-      <c r="B13" s="25">
-        <v>1</v>
+      <c r="B13" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D13" s="25">
         <v>4</v>
       </c>
-      <c r="E13" s="25">
-        <v>1</v>
+      <c r="E13" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="20" customHeight="1">
       <c r="A14" s="6">
         <v>11</v>
       </c>
-      <c r="B14" s="6">
-        <v>3</v>
+      <c r="B14" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D14" s="6">
         <v>4</v>
       </c>
-      <c r="E14" s="6">
-        <v>5</v>
+      <c r="E14" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="20" customHeight="1">
       <c r="A15" s="25">
         <v>12</v>
       </c>
-      <c r="B15" s="25">
-        <v>9</v>
+      <c r="B15" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D15" s="25">
         <v>4</v>
       </c>
-      <c r="E15" s="25">
-        <v>5000</v>
+      <c r="E15" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1">
       <c r="A16" s="6">
         <v>13</v>
       </c>
-      <c r="B16" s="6">
-        <v>1</v>
+      <c r="B16" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" s="6">
         <v>5</v>
       </c>
-      <c r="E16" s="6">
-        <v>1</v>
+      <c r="E16" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="20" customHeight="1">
       <c r="A17" s="25">
         <v>14</v>
       </c>
-      <c r="B17" s="25">
-        <v>3</v>
+      <c r="B17" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D17" s="25">
         <v>5</v>
       </c>
-      <c r="E17" s="25">
-        <v>5</v>
+      <c r="E17" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="20" customHeight="1">
       <c r="A18" s="6">
         <v>15</v>
       </c>
-      <c r="B18" s="6">
-        <v>9</v>
+      <c r="B18" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D18" s="6">
         <v>5</v>
       </c>
-      <c r="E18" s="6">
-        <v>5000</v>
+      <c r="E18" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="20" customHeight="1">
       <c r="A19" s="25">
         <v>16</v>
       </c>
-      <c r="B19" s="25">
-        <v>1</v>
+      <c r="B19" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D19" s="25">
         <v>6</v>
       </c>
-      <c r="E19" s="25">
-        <v>1</v>
+      <c r="E19" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="20" customHeight="1">
       <c r="A20" s="6">
         <v>17</v>
       </c>
-      <c r="B20" s="6">
-        <v>3</v>
+      <c r="B20" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D20" s="6">
         <v>6</v>
       </c>
-      <c r="E20" s="6">
-        <v>5</v>
+      <c r="E20" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="20" customHeight="1">
       <c r="A21" s="25">
         <v>18</v>
       </c>
-      <c r="B21" s="25">
-        <v>9</v>
+      <c r="B21" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D21" s="25">
         <v>6</v>
       </c>
-      <c r="E21" s="25">
-        <v>5000</v>
+      <c r="E21" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="20" customHeight="1">
       <c r="A22" s="6">
         <v>19</v>
       </c>
-      <c r="B22" s="6">
-        <v>1</v>
+      <c r="B22" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D22" s="6">
         <v>7</v>
       </c>
-      <c r="E22" s="6">
-        <v>1</v>
+      <c r="E22" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="20" customHeight="1">
       <c r="A23" s="25">
         <v>20</v>
       </c>
-      <c r="B23" s="25">
-        <v>3</v>
+      <c r="B23" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D23" s="25">
         <v>7</v>
       </c>
-      <c r="E23" s="25">
-        <v>5</v>
+      <c r="E23" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="20" customHeight="1">
       <c r="A24" s="6">
         <v>21</v>
       </c>
-      <c r="B24" s="6">
-        <v>9</v>
+      <c r="B24" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D24" s="6">
         <v>7</v>
       </c>
-      <c r="E24" s="6">
-        <v>5000</v>
+      <c r="E24" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="20" customHeight="1">
       <c r="A25" s="25">
         <v>22</v>
       </c>
-      <c r="B25" s="25">
-        <v>1</v>
+      <c r="B25" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D25" s="25">
         <v>8</v>
       </c>
-      <c r="E25" s="25">
-        <v>1</v>
+      <c r="E25" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="20" customHeight="1">
       <c r="A26" s="6">
         <v>23</v>
       </c>
-      <c r="B26" s="6">
-        <v>3</v>
+      <c r="B26" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D26" s="6">
         <v>8</v>
       </c>
-      <c r="E26" s="6">
-        <v>5</v>
+      <c r="E26" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="20" customHeight="1">
       <c r="A27" s="25">
         <v>24</v>
       </c>
-      <c r="B27" s="25">
-        <v>9</v>
+      <c r="B27" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D27" s="25">
         <v>8</v>
       </c>
-      <c r="E27" s="25">
-        <v>5000</v>
+      <c r="E27" s="6" t="s">
+        <v>328</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="17"/>
@@ -5657,44 +7482,44 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="20" customHeight="1">
@@ -6314,230 +8139,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="17"/>
-  <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.6640625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="20" customHeight="1">
-      <c r="A4" s="6">
-        <v>1</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="6">
-        <v>10</v>
-      </c>
-      <c r="D4" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="20" customHeight="1">
-      <c r="A5" s="25">
-        <v>2</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="25">
-        <v>11</v>
-      </c>
-      <c r="D5" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="20" customHeight="1">
-      <c r="A6" s="6">
-        <v>3</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="6">
-        <v>12</v>
-      </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="17"/>
-  <cols>
-    <col min="1" max="1" width="17" style="1" customWidth="1"/>
-    <col min="2" max="6" width="32" style="1" customWidth="1"/>
-    <col min="7" max="8" width="60" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.6640625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="H2" s="23" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="50" customHeight="1">
-      <c r="A4" s="31">
-        <v>1</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>42</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>